--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_rarity_info[稀有度].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_rarity_info[稀有度].xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="RarityInfo" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
   <si>
     <t>id</t>
   </si>
@@ -86,55 +86,73 @@
     <t>备注</t>
   </si>
   <si>
+    <t>#D4D4D4,#9E9E9E</t>
+  </si>
+  <si>
+    <t>#F5F5F5,#C0C0C0</t>
+  </si>
+  <si>
     <t>#B9B9B9</t>
   </si>
   <si>
-    <t>#E0E0E0</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
+    <t>#8BC46E,#578042</t>
+  </si>
+  <si>
+    <t>#D2EFC4,#8FB87E</t>
+  </si>
+  <si>
     <t>#71A258</t>
   </si>
   <si>
-    <t>#B7D4A9</t>
-  </si>
-  <si>
     <t>R</t>
   </si>
   <si>
+    <t>#6A7BC8,#344592</t>
+  </si>
+  <si>
+    <t>#D1D9FD,#8B93C0</t>
+  </si>
+  <si>
     <t>#4F60AD</t>
   </si>
   <si>
-    <t>#B6BEE2</t>
-  </si>
-  <si>
     <t>SR</t>
   </si>
   <si>
+    <t>#A9459A,#75106B</t>
+  </si>
+  <si>
+    <t>#F4BDEA,#AE7BA5</t>
+  </si>
+  <si>
     <t>#8F2A80</t>
   </si>
   <si>
-    <t>#D9A2D0</t>
-  </si>
-  <si>
     <t>SSR</t>
   </si>
   <si>
+    <t>#FFDB5A,#D6A90C</t>
+  </si>
+  <si>
+    <t>#FFFFD8,#E0CF98</t>
+  </si>
+  <si>
     <t>#EFC230</t>
   </si>
   <si>
-    <t>#FFEFBD</t>
-  </si>
-  <si>
     <t>UR</t>
   </si>
   <si>
+    <t>#B0464A,#7A1014</t>
+  </si>
+  <si>
+    <t>#FFB4B8,#D07A7E</t>
+  </si>
+  <si>
     <t>#922B2F</t>
-  </si>
-  <si>
-    <t>#F8999D</t>
   </si>
   <si>
     <t>L</t>
@@ -1227,10 +1245,10 @@
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1239,7 +1257,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1247,16 +1265,16 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5">
         <v>2</v>
@@ -1265,7 +1283,7 @@
         <v>2</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1273,16 +1291,16 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -1291,7 +1309,7 @@
         <v>3</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:8">
@@ -1299,16 +1317,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F7" s="3">
         <v>8</v>
@@ -1317,7 +1335,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="1" spans="1:8">
@@ -1325,16 +1343,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F8" s="3">
         <v>16</v>
@@ -1343,7 +1361,7 @@
         <v>5</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" customFormat="1" spans="1:8">
@@ -1351,16 +1369,16 @@
         <v>6</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F9" s="3">
         <v>32</v>
@@ -1369,7 +1387,7 @@
         <v>6</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_rarity_info[稀有度].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_rarity_info[稀有度].xlsx
@@ -1062,7 +1062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" style="5" min="2" max="2"/>
@@ -1117,6 +1117,16 @@
           <t>CMP_rate</t>
         </is>
       </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>equip_attribute_add</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ascend_time</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1164,6 +1174,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1209,6 +1229,16 @@
       <c r="I3" s="3" t="inlineStr">
         <is>
           <t>魔力召唤增加倍率</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>装备属性加点数量</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>进阶所需时间(秒,按源稀有度;0为满级不可进阶)</t>
         </is>
       </c>
     </row>
@@ -1250,6 +1280,12 @@
       <c r="I4" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="J4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -1289,6 +1325,12 @@
       <c r="I5" s="3" t="n">
         <v>0.5</v>
       </c>
+      <c r="J5" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -1328,6 +1370,12 @@
       <c r="I6" s="3" t="n">
         <v>1</v>
       </c>
+      <c r="J6" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2500</v>
+      </c>
     </row>
     <row r="7" s="5">
       <c r="A7" s="3" t="n">
@@ -1367,6 +1415,12 @@
       <c r="I7" s="3" t="n">
         <v>1.5</v>
       </c>
+      <c r="J7" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K7" t="n">
+        <v>12500</v>
+      </c>
     </row>
     <row r="8" s="5">
       <c r="A8" s="3" t="n">
@@ -1406,6 +1460,12 @@
       <c r="I8" s="3" t="n">
         <v>2</v>
       </c>
+      <c r="J8" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>62500</v>
+      </c>
     </row>
     <row r="9" s="5">
       <c r="A9" s="3" t="n">
@@ -1444,6 +1504,12 @@
       </c>
       <c r="I9" s="3" t="n">
         <v>2.5</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="5"/>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_rarity_info[稀有度].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_rarity_info[稀有度].xlsx
@@ -1122,7 +1122,7 @@
           <t>equip_attribute_add</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>ascend_time</t>
         </is>
@@ -1179,7 +1179,7 @@
           <t>int</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -1236,7 +1236,7 @@
           <t>装备属性加点数量</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>进阶所需时间(秒,按源稀有度;0为满级不可进阶)</t>
         </is>
@@ -1283,8 +1283,8 @@
       <c r="J4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K4" t="n">
-        <v>100</v>
+      <c r="K4" s="3" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="5">
@@ -1328,8 +1328,8 @@
       <c r="J5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="K5" t="n">
-        <v>500</v>
+      <c r="K5" s="3" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="6">
@@ -1373,8 +1373,8 @@
       <c r="J6" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="K6" t="n">
-        <v>2500</v>
+      <c r="K6" s="3" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="7" s="5">
@@ -1418,8 +1418,8 @@
       <c r="J7" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="K7" t="n">
-        <v>12500</v>
+      <c r="K7" s="3" t="n">
+        <v>7200</v>
       </c>
     </row>
     <row r="8" s="5">
@@ -1463,8 +1463,8 @@
       <c r="J8" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="K8" t="n">
-        <v>62500</v>
+      <c r="K8" s="3" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="9" s="5">
@@ -1508,7 +1508,7 @@
       <c r="J9" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Demon Lord Roguelike/Assets/Data/Excel/excel_rarity_info[稀有度].xlsx
+++ b/Demon Lord Roguelike/Assets/Data/Excel/excel_rarity_info[稀有度].xlsx
@@ -1062,7 +1062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="20" customWidth="1" style="5" min="2" max="2"/>
@@ -1509,6 +1509,51 @@
         <v>30</v>
       </c>
       <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>999</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>#1A1A22,#2A1030</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>#3A2A4D,#1C1A26</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>#4A2A5A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>#5A1A3A</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>64</v>
+      </c>
+      <c r="G10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DemonLord</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>0</v>
       </c>
     </row>
